--- a/cost_COA25.xlsx
+++ b/cost_COA25.xlsx
@@ -1,31 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\1_UPM_Z\PYsimul\SMR_model1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66250FB-121A-4C65-ABF9-88688247E83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65929C-4116-4420-8743-EFE0E3CAE065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24780" yWindow="3990" windowWidth="19040" windowHeight="14090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={42662CDF-E58B-41A1-967D-2757D77EE38B}</author>
+    <author>tc={F6CE5B75-89F3-432B-976B-DB49CAC31FF2}</author>
+    <author>tc={F7C3AE83-BDB4-40E8-A76C-02388BB72AF7}</author>
+    <author>tc={9367BEFF-7783-46A2-BBF2-E46A32000F62}</author>
+    <author>tc={EBFC147C-ED72-4808-88C7-56FA8DDA3134}</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{42662CDF-E58B-41A1-967D-2757D77EE38B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    NREL</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="1" shapeId="0" xr:uid="{F6CE5B75-89F3-432B-976B-DB49CAC31FF2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Do not include capital costs for CO2, transportation and storage</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="2" shapeId="0" xr:uid="{F7C3AE83-BDB4-40E8-A76C-02388BB72AF7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Obtained form Danish Energy Agency data</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="3" shapeId="0" xr:uid="{9367BEFF-7783-46A2-BBF2-E46A32000F62}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    NREL</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="4" shapeId="0" xr:uid="{EBFC147C-ED72-4808-88C7-56FA8DDA3134}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    From Danish Energy Agency Data: Gas turbine, combined cycle - back pressure - natural gas - medium</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>technology</t>
   </si>
@@ -67,13 +132,37 @@
   </si>
   <si>
     <t>carbon_cost</t>
+  </si>
+  <si>
+    <t>SMR_CHP</t>
+  </si>
+  <si>
+    <t>Gas_CHP</t>
+  </si>
+  <si>
+    <t>Grid_connect_cost</t>
+  </si>
+  <si>
+    <t>MEUR/Mwe</t>
+  </si>
+  <si>
+    <t>Eur/kWe</t>
+  </si>
+  <si>
+    <t>Average exchange rate in 2015 EUR-USD: 1.11 USD.</t>
+  </si>
+  <si>
+    <t>USD/kWe</t>
+  </si>
+  <si>
+    <t>Gas_CHP2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,16 +178,83 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +262,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -118,9 +326,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{05CE85B9-A5ED-4A64-8CE3-47D02B0E644F}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{BC66E569-D0F4-4C34-86EF-8029D2EE9B03}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{75E27299-F84E-4D11-B0C2-4A7B29365D1F}"/>
+    <cellStyle name="Normal 5" xfId="5" xr:uid="{6D9581D8-4357-4558-BB37-3FB67F13B3A6}"/>
+    <cellStyle name="Normal 6" xfId="7" xr:uid="{55FDDB68-E846-48CF-9A63-704B9E687CE4}"/>
+    <cellStyle name="Normal 7" xfId="1" xr:uid="{F16F861A-3B9C-4CC1-AE4E-4E1270E06217}"/>
+    <cellStyle name="Percent 2" xfId="6" xr:uid="{6F2927DD-BE30-4D05-964F-F27C535E6DB5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -133,6 +373,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="CARLOS OLMOS ALONSO" id="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" userId="S::carlos.olmos.alonso@alumnos.upm.es::b1989f31-5088-41d6-9a36-5ce09ab23a53" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -396,28 +642,49 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A3" dT="2025-04-30T16:35:45.87" personId="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" id="{42662CDF-E58B-41A1-967D-2757D77EE38B}">
+    <text>NREL</text>
+  </threadedComment>
+  <threadedComment ref="B3" dT="2025-04-30T16:12:17.00" personId="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" id="{F6CE5B75-89F3-432B-976B-DB49CAC31FF2}">
+    <text>Do not include capital costs for CO2, transportation and storage</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2025-04-30T16:20:06.67" personId="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" id="{F7C3AE83-BDB4-40E8-A76C-02388BB72AF7}">
+    <text>Obtained form Danish Energy Agency data</text>
+  </threadedComment>
+  <threadedComment ref="A4" dT="2025-04-30T16:35:45.87" personId="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" id="{9367BEFF-7783-46A2-BBF2-E46A32000F62}">
+    <text>NREL</text>
+  </threadedComment>
+  <threadedComment ref="B12" dT="2025-04-30T16:32:25.27" personId="{A30607FB-3F71-47B6-9249-7B2C09B8F7B4}" id="{EBFC147C-ED72-4808-88C7-56FA8DDA3134}">
+    <text>From Danish Energy Agency Data: Gas turbine, combined cycle - back pressure - natural gas - medium</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,9 +726,214 @@
       </c>
       <c r="N1" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
+        <v>9500</v>
+      </c>
+      <c r="C2" s="4">
+        <v>216</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>60</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4">
+        <f>12</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>300</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.93</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5">
+        <f>1354</f>
+        <v>1354</v>
+      </c>
+      <c r="C3" s="5">
+        <v>37</v>
+      </c>
+      <c r="D3" s="6">
+        <f>2.37</f>
+        <v>2.37</v>
+      </c>
+      <c r="E3" s="5">
+        <v>25</v>
+      </c>
+      <c r="F3" s="5">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <f>50</f>
+        <v>50</v>
+      </c>
+      <c r="I3" s="5">
+        <f>450</f>
+        <v>450</v>
+      </c>
+      <c r="J3" s="5">
+        <v>649</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="5">
+        <f>B12</f>
+        <v>1062.3093452820001</v>
+      </c>
+      <c r="C4" s="5">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6">
+        <f>2.37</f>
+        <v>2.37</v>
+      </c>
+      <c r="E4" s="5">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <f>50</f>
+        <v>50</v>
+      </c>
+      <c r="I4" s="5">
+        <f>450</f>
+        <v>450</v>
+      </c>
+      <c r="J4" s="5">
+        <v>100</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="10">
+        <v>0.74436090259999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="10">
+        <v>0.21267454360000004</v>
+      </c>
+      <c r="C9" s="11">
+        <v>4.7851772310000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <f>B8+B9</f>
+        <v>0.95703544620000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <f>B10*10^3</f>
+        <v>957.03544620000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="9">
+        <f>B11*B14</f>
+        <v>1062.3093452820001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:15" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1.1100000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>